--- a/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>AOUT</t>
   </si>
@@ -656,85 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,56 +746,62 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>57900</v>
+      </c>
+      <c r="F8" s="3">
         <v>43400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>42200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>50900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>54400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>43700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>45900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>70100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>70800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>60800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>64500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>82600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>79100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>50500</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,56 +811,62 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>31400</v>
+      </c>
+      <c r="F9" s="3">
         <v>23700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>23100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>26900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>28500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>24600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>25800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>38000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>37700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>31800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>35800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>45300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>42000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>26700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -862,56 +876,62 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>26500</v>
+      </c>
+      <c r="F10" s="3">
         <v>19700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>19100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>24000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>25900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>19100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>20100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>32100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>33100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>29000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>28700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>37300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>37100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>23800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +941,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,56 +970,58 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="E12" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="F12" s="3">
         <v>1600</v>
       </c>
       <c r="G12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H12" s="3">
         <v>1600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J12" s="3">
         <v>1800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M12" s="3">
-        <v>700</v>
       </c>
       <c r="N12" s="3">
         <v>1500</v>
       </c>
       <c r="O12" s="3">
+        <v>700</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,8 +1031,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,35 +1096,41 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>67800</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1103,11 +1143,11 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1121,8 +1161,14 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1180,8 +1226,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,56 +1252,58 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>58000</v>
+      </c>
+      <c r="F17" s="3">
         <v>47500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>46200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>53900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>54600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>49200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>116700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>65400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>65500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>56500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>63200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>72500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>69500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>48000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,56 +1313,62 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-4000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-5500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-70800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>4700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>10100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>9600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2500</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1378,14 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,56 +1407,58 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1400,56 +1468,62 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>4300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-66200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>9100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>10100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>8500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>6100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>14900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>14800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>8300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,8 +1533,14 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1518,56 +1598,62 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-5500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-70600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>9700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,56 +1663,62 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-100</v>
       </c>
       <c r="G24" s="3">
         <v>-200</v>
       </c>
       <c r="H24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>6100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1636,8 +1728,14 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,56 +1793,62 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-76700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>3800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>8000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>7300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,56 +1858,62 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-76700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>8000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>7300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1923,14 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1988,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +2053,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2118,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,56 +2183,62 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2108,56 +2248,62 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-76700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>8000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>7300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,8 +2313,14 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,56 +2378,62 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-76700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>8000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>7300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,61 +2443,67 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2513,14 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2542,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,55 +2567,57 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F41" s="3">
         <v>18700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>22000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>21700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>16400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>19500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>22800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>32600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>56300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>60800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>45500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>33900</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
@@ -2454,8 +2628,14 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2513,56 +2693,62 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>40700</v>
+      </c>
+      <c r="F43" s="3">
         <v>24800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>28100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>26600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>33800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>25000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>30100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>46100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>49800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>33500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>42400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>56100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>58000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>42100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,56 +2758,62 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>109100</v>
+      </c>
+      <c r="F44" s="3">
         <v>104900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>99700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>105500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>111400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>120600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>121700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>119600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>105000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>92000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>74300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>73700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>73600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>69600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,56 +2823,62 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F45" s="3">
         <v>7900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>7800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>9700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>11300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>10800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>8500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>9700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>11200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>9000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,56 +2888,62 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>164300</v>
+      </c>
+      <c r="F46" s="3">
         <v>156300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>157600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>163400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>172900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>173900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>179800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>198100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>198500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>190900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>179800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>178400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>168300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>115200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,8 +2953,14 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2808,56 +3018,62 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>32500</v>
+      </c>
+      <c r="F48" s="3">
         <v>33000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>33700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>34400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>35100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>35800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>34500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>37900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>37200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>35900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>36400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>36200</v>
       </c>
       <c r="O48" s="3">
         <v>36400</v>
       </c>
       <c r="P48" s="3">
+        <v>36200</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>36400</v>
+      </c>
+      <c r="R48" s="3">
         <v>12300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2867,56 +3083,62 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46400</v>
+      </c>
+      <c r="F49" s="3">
         <v>49200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>52000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>55000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>58100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>60700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>63200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>108100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>111300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>114600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>118000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>121900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>125900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>129700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,8 +3148,14 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3213,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,56 +3278,62 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>500</v>
+      </c>
+      <c r="F52" s="3">
         <v>600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
       <c r="J52" s="3">
+        <v>400</v>
+      </c>
+      <c r="K52" s="3">
+        <v>300</v>
+      </c>
+      <c r="L52" s="3">
         <v>7300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>7400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>7200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>7100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3600</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,8 +3343,14 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,8 +3408,14 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3171,47 +3423,47 @@
         <v>239100</v>
       </c>
       <c r="E54" s="3">
+        <v>243700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>239100</v>
+      </c>
+      <c r="G54" s="3">
         <v>243600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>253200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>266500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>270700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>277800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>351400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>354400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>348700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>341300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>341400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>335400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>260800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3473,14 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3502,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,56 +3527,58 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>17800</v>
+      </c>
+      <c r="F57" s="3">
         <v>15600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>8800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>13600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>20500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>20100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>20200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>16000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>15800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>19900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>15100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,8 +3588,14 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3385,56 +3653,62 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F59" s="3">
         <v>13600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>11500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>14000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>14800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>15100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>13400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>20500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>21100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>20300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>20300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>22200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>20800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>15800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,56 +3718,62 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>34000</v>
+      </c>
+      <c r="F60" s="3">
         <v>29200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>23000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>24100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>28600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>27000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>40900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>41200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>40400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>36300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>38100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>40700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>31000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,8 +3783,14 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3512,26 +3798,26 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>4600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>9600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>19600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>19600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>24700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3562,56 +3848,62 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F62" s="3">
         <v>23900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>24100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>24300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>24600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>24800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>23100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>23600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>24000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>24400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>25000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>25600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>25900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3913,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3978,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +4043,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,56 +4108,62 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>57700</v>
+      </c>
+      <c r="F66" s="3">
         <v>53000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>51700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>58000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>67700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>72900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>74800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>64500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>65200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>64900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>61400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>63700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>66600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>33400</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4173,14 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4202,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4263,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4328,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4057,8 +4393,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,53 +4458,59 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-66400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-66500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-62400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-58500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-55700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-56000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-50400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>26300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>22600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>18000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>14500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>13300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>5300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4523,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4588,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4653,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,56 +4718,62 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>182400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>186000</v>
+      </c>
+      <c r="F76" s="3">
         <v>186100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>191900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>195200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>198800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>197800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>203000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>286900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>289300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>283800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>279900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>277700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>268800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>227300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4783,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,61 +4848,67 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,56 +4918,62 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-76700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>8000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>7300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4983,14 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,8 +5012,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4628,44 +5026,44 @@
         <v>4000</v>
       </c>
       <c r="F83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H83" s="3">
         <v>4300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>4100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4400</v>
       </c>
       <c r="J83" s="3">
         <v>4200</v>
       </c>
       <c r="K83" s="3">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="L83" s="3">
         <v>4200</v>
       </c>
       <c r="M83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O83" s="3">
         <v>4700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>4700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>5100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>5400</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4675,8 +5073,14 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +5138,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +5203,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5268,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5333,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,56 +5398,62 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F89" s="3">
         <v>5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>6400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>18100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>5100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>8200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-22100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>16300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>12600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,8 +5463,14 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,55 +5492,57 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-800</v>
       </c>
       <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-900</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5111,8 +5553,14 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5618,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,40 +5683,46 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-28900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-1100</v>
       </c>
       <c r="N94" s="3">
         <v>-1000</v>
@@ -5273,11 +5733,11 @@
       <c r="P94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-1000</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5288,8 +5748,14 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,8 +5777,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5370,8 +5838,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5903,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5968,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,56 +6033,62 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-7600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-5600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-11800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-5500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>17400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-7000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>31100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5606,8 +6098,14 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5665,56 +6163,62 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-9800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-23700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-4500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>15300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>11600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>33900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5722,6 +6226,12 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>AOUT</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,62 +753,68 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>46300</v>
+      </c>
+      <c r="F8" s="3">
         <v>53400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>57900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>43400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>42200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>50900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>54400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>43700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>45900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>70100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>70800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>60800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>64500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>82600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>79100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>50500</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -817,62 +824,68 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F9" s="3">
         <v>30600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>31400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>23700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>23100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>26900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>28500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>24600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>25800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>38000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>37700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>31800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>35800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>45300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>42000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>26700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,62 +895,68 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F10" s="3">
         <v>22800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>26500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>19700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>19100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>24000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>25900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>19100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>20100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>32100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>33100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>29000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>28700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>37300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>37100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>23800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +966,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,62 +997,64 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G12" s="3">
         <v>1700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1500</v>
       </c>
       <c r="H12" s="3">
         <v>1600</v>
       </c>
       <c r="I12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L12" s="3">
         <v>1800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1500</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O12" s="3">
-        <v>700</v>
       </c>
       <c r="P12" s="3">
         <v>1500</v>
       </c>
       <c r="Q12" s="3">
+        <v>700</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S12" s="3">
         <v>1900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1200</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1064,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,41 +1135,47 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>67800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1149,11 +1188,11 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1167,8 +1206,14 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1232,8 +1277,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,62 +1305,64 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>51800</v>
+      </c>
+      <c r="F17" s="3">
         <v>56300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>58000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>47500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>46200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>53900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>54600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>49200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>116700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>65400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>65500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>56500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>63200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>72500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>69500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>48000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,62 +1372,68 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-70800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>4300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>10100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>9600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1443,14 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,62 +1474,64 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,62 +1541,68 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>4000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-66200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>9100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>10100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>8500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>6100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>14900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>14800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>8300</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1612,14 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1604,62 +1683,68 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2900</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-70600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>4300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>10300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>9700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,8 +1754,14 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1678,53 +1769,53 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
       </c>
       <c r="I24" s="3">
         <v>-200</v>
       </c>
       <c r="J24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>6100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,8 +1825,14 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,62 +1896,68 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-76700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>8000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>7300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,62 +1967,68 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-76700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>8000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>7300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +2038,14 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2109,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2180,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2251,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,62 +2322,68 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,62 +2393,68 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-76700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>8000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>7300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2464,14 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,62 +2535,68 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-76700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>8000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>7300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,67 +2606,73 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2682,14 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2713,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,61 +2740,63 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F41" s="3">
         <v>15900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>22000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>21700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>16400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>19500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>22800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>32600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>56300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>60800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>45500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>33900</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
+      <c r="T41" s="3">
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
@@ -2634,8 +2807,14 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2699,62 +2878,68 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F43" s="3">
         <v>27500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>40700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>24800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>28100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>26600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>33800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>25000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>30100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>46100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>49800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>33500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>42400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>56100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>58000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>42100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2764,62 +2949,68 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>93300</v>
+      </c>
+      <c r="F44" s="3">
         <v>100000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>109100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>104900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>99700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>105500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>111400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>120600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>121700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>119600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>105000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>92000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>74300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>73700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>73600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>69600</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2829,62 +3020,68 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F45" s="3">
         <v>6600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>7900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>7800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>9700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>11300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>10800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>8500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>9700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>9000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3500</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,62 +3091,68 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>162300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>155400</v>
+      </c>
+      <c r="F46" s="3">
         <v>149900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>164300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>156300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>157600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>163400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>172900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>173900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>179800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>198100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>198500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>190900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>179800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>178400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>168300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>115200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3162,14 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3024,62 +3233,68 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>44600</v>
+      </c>
+      <c r="F48" s="3">
         <v>45400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>32500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>33000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>33700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>34400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>35100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>35800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>34500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>37900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>37200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>35900</v>
-      </c>
-      <c r="O48" s="3">
-        <v>36400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>36200</v>
       </c>
       <c r="Q48" s="3">
         <v>36400</v>
       </c>
       <c r="R48" s="3">
+        <v>36200</v>
+      </c>
+      <c r="S48" s="3">
+        <v>36400</v>
+      </c>
+      <c r="T48" s="3">
         <v>12300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,62 +3304,68 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>40200</v>
+      </c>
+      <c r="F49" s="3">
         <v>43300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>46400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>49200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>52000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>55000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>58100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>60700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>63200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>108100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>111300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>114600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>118000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>121900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>125900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>129700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3154,8 +3375,14 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3446,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,62 +3517,68 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>400</v>
+      </c>
+      <c r="F52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>300</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
       <c r="J52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
       </c>
       <c r="L52" s="3">
+        <v>400</v>
+      </c>
+      <c r="M52" s="3">
+        <v>300</v>
+      </c>
+      <c r="N52" s="3">
         <v>7300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>7400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>7200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>7100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3600</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3588,14 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,62 +3659,68 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>239100</v>
+        <v>244800</v>
       </c>
       <c r="E54" s="3">
-        <v>243700</v>
+        <v>240600</v>
       </c>
       <c r="F54" s="3">
         <v>239100</v>
       </c>
       <c r="G54" s="3">
+        <v>243700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>239100</v>
+      </c>
+      <c r="I54" s="3">
         <v>243600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>253200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>266500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>270700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>277800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>351400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>354400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>348700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>341300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>341400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>335400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>260800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3730,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3761,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,62 +3788,64 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F57" s="3">
         <v>9200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>17800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>15600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>11500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>13500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>13600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>20500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>20100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>20200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>16000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>15800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>19900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>15100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3855,14 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3659,62 +3926,68 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F59" s="3">
         <v>13800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>16200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>13600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>11500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>14000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>14800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>15100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>13400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>20500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>21100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>20300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>20300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>22200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>20800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>15800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,62 +3997,68 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>29400</v>
+      </c>
+      <c r="F60" s="3">
         <v>23000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>34000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>29200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>24100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>23600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>28600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>27000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>40900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>41200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>40400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>36300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>38100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>40700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>31000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,8 +4068,14 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3804,26 +4089,26 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>4600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>19600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>19600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>24700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3854,62 +4139,68 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>33300</v>
+      </c>
+      <c r="F62" s="3">
         <v>33600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>23700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>23900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>24100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>24300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>24600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>24800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>23100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>23600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>24000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>24400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>25000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>25600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>25900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4210,14 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4281,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4352,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,62 +4423,68 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>62700</v>
+      </c>
+      <c r="F66" s="3">
         <v>56700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>57700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>53000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>51700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>58000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>67700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>72900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>74800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>64500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>65200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>64900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>61400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>63700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>66600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>33400</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4494,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4525,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4592,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4663,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4734,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,59 +4805,65 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-74600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-69300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-66400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-66500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-62400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-58500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-55700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-56000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-50400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>26300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>22600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>18000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>14500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>13300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>5300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4529,8 +4876,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4947,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +5018,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,62 +5089,68 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>175700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>177900</v>
+      </c>
+      <c r="F76" s="3">
         <v>182400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>186000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>186100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>191900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>195200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>198800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>197800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>203000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>286900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>289300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>283800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>279900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>277700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>268800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>227300</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +5160,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5231,73 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,62 +5307,68 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-76700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>8000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>7300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4989,8 +5378,14 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,16 +5409,18 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4000</v>
+        <v>3300</v>
       </c>
       <c r="E83" s="3">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="F83" s="3">
         <v>4000</v>
@@ -5032,44 +5429,44 @@
         <v>4000</v>
       </c>
       <c r="H83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J83" s="3">
         <v>4300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>4100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4400</v>
       </c>
       <c r="L83" s="3">
         <v>4200</v>
       </c>
       <c r="M83" s="3">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="N83" s="3">
         <v>4200</v>
       </c>
       <c r="O83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>4700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>4700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>5100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>5400</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5079,8 +5476,14 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5547,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5618,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5689,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5760,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,62 +5831,68 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F89" s="3">
         <v>13000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-8400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>18100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>5100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>8200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-22100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>16300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>12600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>3900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5902,14 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,61 +5933,63 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-800</v>
       </c>
       <c r="R91" s="3">
         <v>-900</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-900</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5559,8 +6000,14 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +6071,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,46 +6142,52 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3700</v>
+        <v>-1100</v>
       </c>
       <c r="E94" s="3">
         <v>-700</v>
       </c>
       <c r="F94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-28900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-1100</v>
       </c>
       <c r="P94" s="3">
         <v>-1000</v>
@@ -5739,11 +6198,11 @@
       <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T94" s="3">
+        <v>-1000</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5754,8 +6213,14 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6244,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6311,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6382,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6453,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,62 +6524,68 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-7600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-5600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-11800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-5500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>17400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-7000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>31100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,8 +6595,14 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6169,62 +6666,68 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F102" s="3">
         <v>7500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-10300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-9800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-23700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>15300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>11600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>33900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6735,12 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>AOUT</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,65 +760,68 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E8" s="3">
         <v>41600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>53400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>57900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>43400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>42200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>50900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>54400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>43700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>45900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>70100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>70800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>60800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>64500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>82600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>79100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>50500</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -830,65 +834,68 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E9" s="3">
         <v>22700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>38000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>37700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>35800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>45300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>42000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,65 +908,68 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E10" s="3">
         <v>18900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>32100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>33100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>37100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,65 +1012,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>1700</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1800</v>
       </c>
       <c r="F12" s="3">
         <v>1800</v>
       </c>
       <c r="G12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H12" s="3">
         <v>1700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1600</v>
       </c>
       <c r="K12" s="3">
         <v>1600</v>
       </c>
       <c r="L12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M12" s="3">
         <v>1800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1400</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1500</v>
       </c>
       <c r="P12" s="3">
         <v>1500</v>
       </c>
       <c r="Q12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1200</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,16 +1158,19 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1161,11 +1181,11 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1173,12 +1193,12 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>67800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1194,8 +1214,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1212,31 +1232,34 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,65 +1333,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E17" s="3">
         <v>44200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>51800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>56300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>58000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>53900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>49200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>116700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>65400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>65500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>63200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>72500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>69500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>48000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,65 +1405,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-100</v>
-      </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-70800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,49 +1509,50 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>400</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
@@ -1527,14 +1561,14 @@
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,65 +1581,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1000</v>
+        <v>6400</v>
       </c>
       <c r="E21" s="3">
-        <v>-1200</v>
+        <v>800</v>
       </c>
       <c r="F21" s="3">
-        <v>1100</v>
+        <v>-1300</v>
       </c>
       <c r="G21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H21" s="3">
         <v>4000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
+        <v>100</v>
+      </c>
+      <c r="K21" s="3">
         <v>1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-66200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>14800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8300</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,31 +1655,34 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1689,65 +1729,68 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2900</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-4100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-70600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,8 +1803,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1769,56 +1815,56 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,65 +1951,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-76700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,65 +2025,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-76700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1800</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,49 +2395,52 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
@@ -2379,14 +2449,14 @@
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2399,65 +2469,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-76700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1800</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,65 +2617,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-76700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1800</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,64 +2828,65 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E41" s="3">
         <v>23500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>32600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>56300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>60800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>33900</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
@@ -2813,8 +2900,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2884,65 +2974,68 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E43" s="3">
         <v>26600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>33800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>30100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>46100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>49800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>33500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>42400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>56100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>58000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>42100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2955,65 +3048,68 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>106700</v>
+        <v>111600</v>
       </c>
       <c r="E44" s="3">
-        <v>93300</v>
+        <v>108800</v>
       </c>
       <c r="F44" s="3">
-        <v>100000</v>
+        <v>97600</v>
       </c>
       <c r="G44" s="3">
-        <v>109100</v>
+        <v>103800</v>
       </c>
       <c r="H44" s="3">
-        <v>104900</v>
+        <v>112700</v>
       </c>
       <c r="I44" s="3">
-        <v>99700</v>
+        <v>110000</v>
       </c>
       <c r="J44" s="3">
+        <v>104000</v>
+      </c>
+      <c r="K44" s="3">
         <v>105500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>111400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>120600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>121700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>119600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>105000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>92000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>74300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>73700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>73600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>69600</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,65 +3122,68 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>5600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>6400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>6600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>6000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>7800</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>9700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3500</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,65 +3196,68 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>174200</v>
+      </c>
+      <c r="E46" s="3">
         <v>162300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>149900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>164300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>156300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>157600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>163400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>172900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>173900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>179800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>198100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>198500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>190900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>179800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>178400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>168300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>115200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,31 +3270,34 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3239,65 +3344,68 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E48" s="3">
         <v>44200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>44600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>36400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3310,65 +3418,68 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E49" s="3">
         <v>37900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>40200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>43300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>46400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>49200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>52000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>55000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>58100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>60700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>63200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>108100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>111300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>114600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>118000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>121900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>125900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>129700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,8 +3492,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,28 +3640,31 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
       </c>
       <c r="F52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G52" s="3">
         <v>500</v>
       </c>
       <c r="H52" s="3">
+        <v>500</v>
+      </c>
+      <c r="I52" s="3">
         <v>600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>300</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
@@ -3553,35 +3673,35 @@
         <v>300</v>
       </c>
       <c r="L52" s="3">
+        <v>300</v>
+      </c>
+      <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,65 +3788,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>254100</v>
+      </c>
+      <c r="E54" s="3">
         <v>244800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>240600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>239100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>243700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>239100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>243600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>253200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>266500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>270700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>277800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>351400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>354400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>348700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>341300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>341400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>335400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>260800</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,65 +3920,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E57" s="3">
         <v>18100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,31 +3992,34 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3932,65 +4066,68 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>18000</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
-        <v>15200</v>
+        <v>1400</v>
       </c>
       <c r="F59" s="3">
-        <v>13800</v>
+        <v>1200</v>
       </c>
       <c r="G59" s="3">
-        <v>16200</v>
+        <v>1100</v>
       </c>
       <c r="H59" s="3">
-        <v>13600</v>
+        <v>900</v>
       </c>
       <c r="I59" s="3">
-        <v>11500</v>
+        <v>900</v>
       </c>
       <c r="J59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K59" s="3">
         <v>14000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21100</v>
-      </c>
-      <c r="P59" s="3">
-        <v>20300</v>
       </c>
       <c r="Q59" s="3">
         <v>20300</v>
       </c>
       <c r="R59" s="3">
+        <v>20300</v>
+      </c>
+      <c r="S59" s="3">
         <v>22200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15800</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,65 +4140,68 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E60" s="3">
         <v>36100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>40700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>31000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4074,44 +4214,47 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>32600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="I61" s="3">
-        <v>4600</v>
+        <v>23800</v>
       </c>
       <c r="J61" s="3">
+        <v>28700</v>
+      </c>
+      <c r="K61" s="3">
         <v>9600</v>
-      </c>
-      <c r="K61" s="3">
-        <v>19600</v>
       </c>
       <c r="L61" s="3">
         <v>19600</v>
       </c>
       <c r="M61" s="3">
+        <v>19600</v>
+      </c>
+      <c r="N61" s="3">
         <v>24700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4145,65 +4288,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>33000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>33300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>33600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>23700</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>23900</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
-        <v>24100</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>24300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,65 +4584,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E66" s="3">
         <v>69100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>62700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>56700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>51700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>74800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>64900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>61400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>63700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>66600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33400</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,62 +4982,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-73900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-77000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-74600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-69300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-66400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-66500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-62400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-58500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-55700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-56000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-50400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>22600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,65 +5278,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>178900</v>
+      </c>
+      <c r="E76" s="3">
         <v>175700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>177900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>182400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>186000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>191900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>195200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>198800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>197800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>203000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>286900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>289300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>283800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>279900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>277700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>268800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>227300</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,65 +5505,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-76700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1800</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,43 +5609,44 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3300</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
+        <v>800</v>
+      </c>
+      <c r="F83" s="3">
+        <v>700</v>
+      </c>
+      <c r="G83" s="3">
+        <v>700</v>
+      </c>
+      <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M83" s="3">
         <v>4200</v>
       </c>
-      <c r="F83" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4200</v>
       </c>
       <c r="O83" s="3">
         <v>4200</v>
@@ -5456,20 +5655,20 @@
         <v>4200</v>
       </c>
       <c r="Q83" s="3">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="R83" s="3">
         <v>4700</v>
       </c>
       <c r="S83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T83" s="3">
         <v>5100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5400</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,65 +6051,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>16300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,65 +6155,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1100</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F91" s="3">
-        <v>-3700</v>
+        <v>-500</v>
       </c>
       <c r="G91" s="3">
-        <v>-900</v>
+        <v>-3300</v>
       </c>
       <c r="H91" s="3">
-        <v>-800</v>
+        <v>-400</v>
       </c>
       <c r="I91" s="3">
         <v>-600</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1900</v>
       </c>
       <c r="N91" s="3">
         <v>-1900</v>
       </c>
       <c r="O91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1800</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q91" s="3">
         <v>-1000</v>
       </c>
       <c r="R91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S91" s="3">
         <v>-900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-900</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,65 +6375,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6219,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,31 +6479,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,8 +6773,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6539,56 +6785,56 @@
         <v>-800</v>
       </c>
       <c r="E100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>17400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>31100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6601,31 +6847,34 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6672,65 +6921,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-23700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>33900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>AOUT</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,68 +764,71 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E8" s="3">
         <v>60200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>41600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>46300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>53400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>57900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>43400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>42200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>50900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>54400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>43700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>45900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>70100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>60800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>64500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>82600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>79100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>50500</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -837,68 +841,71 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E9" s="3">
         <v>31300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>38000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>37700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>31800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>35800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>45300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>42000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26700</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -911,68 +918,71 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E10" s="3">
         <v>28900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>18900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>26500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>32100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>33100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>28700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>37300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>37100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23800</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,8 +1026,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,59 +1036,59 @@
         <v>1900</v>
       </c>
       <c r="E12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F12" s="3">
         <v>1700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1800</v>
       </c>
       <c r="G12" s="3">
         <v>1800</v>
       </c>
       <c r="H12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I12" s="3">
         <v>1700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1500</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1600</v>
       </c>
       <c r="L12" s="3">
         <v>1600</v>
       </c>
       <c r="M12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1400</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1500</v>
       </c>
       <c r="Q12" s="3">
         <v>1500</v>
       </c>
       <c r="R12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,8 +1178,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1184,11 +1204,11 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
@@ -1196,12 +1216,12 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>67800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1217,8 +1237,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1235,22 +1255,25 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="E15" s="3">
         <v>3300</v>
       </c>
       <c r="F15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G15" s="3">
         <v>4200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4000</v>
       </c>
       <c r="H15" s="3">
         <v>4000</v>
@@ -1262,7 +1285,7 @@
         <v>4000</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1309,8 +1332,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,68 +1360,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E17" s="3">
         <v>57200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>44200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>56300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>58000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>53900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>49200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>116700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>65400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>65500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>63200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>72500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>69500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>48000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,68 +1435,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>300</v>
+      </c>
+      <c r="E18" s="3">
         <v>3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2900</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-4100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-70800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,52 +1543,53 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
@@ -1564,14 +1598,14 @@
         <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,68 +1618,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E21" s="3">
         <v>6400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-66200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>14900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8300</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,35 +1695,38 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
         <v>-100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1732,68 +1772,71 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
         <v>3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2900</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-4100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-70600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2900</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1806,68 +1849,71 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1880,8 +1926,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,68 +2003,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
         <v>3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-76700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1800</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,68 +2080,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
         <v>3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-76700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1800</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2102,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,52 +2465,55 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
@@ -2452,14 +2522,14 @@
         <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,68 +2542,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
         <v>3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-76700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1800</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,68 +2696,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
         <v>3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-76700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1800</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,73 +2773,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,67 +2915,68 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E41" s="3">
         <v>14200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>32600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>56300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>60800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>45500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>33900</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
+      <c r="V41" s="3">
+        <v>0</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
@@ -2903,8 +2990,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2977,68 +3067,71 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E43" s="3">
         <v>43500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>33800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>49800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>33500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>42400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>56100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>42100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3051,68 +3144,71 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>111600</v>
+        <v>116400</v>
       </c>
       <c r="E44" s="3">
+        <v>113000</v>
+      </c>
+      <c r="F44" s="3">
         <v>108800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>97600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>103800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>112700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>110000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>104000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>105500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>111400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>120600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>121700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>119600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>105000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>92000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>74300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>73700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>73600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>69600</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3125,8 +3221,11 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3151,42 +3250,42 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>9700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3500</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,68 +3298,71 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E46" s="3">
         <v>174200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>162300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>155400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>149900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>164300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>156300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>157600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>163400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>172900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>173900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>179800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>198100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>198500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>190900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>179800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>178400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>168300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>115200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3299,8 +3404,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3347,68 +3452,71 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E48" s="3">
         <v>43700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>44200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>36200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>36400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12300</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3421,68 +3529,71 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E49" s="3">
         <v>35900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>40200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>43300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>49200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>52000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>55000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>58100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>60700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>63200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>108100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>111300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>114600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>118000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>121900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>125900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>129700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3495,8 +3606,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,8 +3760,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3652,22 +3772,22 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
       </c>
       <c r="G52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H52" s="3">
         <v>500</v>
       </c>
       <c r="I52" s="3">
+        <v>500</v>
+      </c>
+      <c r="J52" s="3">
         <v>600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
@@ -3676,35 +3796,35 @@
         <v>300</v>
       </c>
       <c r="M52" s="3">
+        <v>300</v>
+      </c>
+      <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3600</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3837,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,68 +3914,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>245900</v>
+      </c>
+      <c r="E54" s="3">
         <v>254100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>244800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>240600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>239100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>243700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>239100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>243600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>253200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>266500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>270700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>277800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>351400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>354400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>348700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>341300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>341400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>335400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>260800</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,68 +4051,69 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E57" s="3">
         <v>25400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,34 +4126,37 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E58" s="3">
         <v>1400</v>
       </c>
       <c r="F58" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G58" s="3">
         <v>1300</v>
       </c>
       <c r="H58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I58" s="3">
         <v>1000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>900</v>
       </c>
       <c r="J58" s="3">
         <v>900</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4069,68 +4203,71 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
         <v>1400</v>
       </c>
       <c r="F59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>900</v>
       </c>
       <c r="I59" s="3">
         <v>900</v>
       </c>
       <c r="J59" s="3">
+        <v>900</v>
+      </c>
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21100</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>20300</v>
       </c>
       <c r="R59" s="3">
         <v>20300</v>
       </c>
       <c r="S59" s="3">
+        <v>20300</v>
+      </c>
+      <c r="T59" s="3">
         <v>22200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15800</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,68 +4280,71 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E60" s="3">
         <v>42600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>41200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>40400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>40700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,47 +4357,50 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E61" s="3">
         <v>32600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>19600</v>
       </c>
       <c r="M61" s="3">
         <v>19600</v>
       </c>
       <c r="N61" s="3">
+        <v>19600</v>
+      </c>
+      <c r="O61" s="3">
         <v>24700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4291,8 +4434,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4308,8 +4454,8 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -4318,41 +4464,41 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>24300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4365,8 +4511,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,68 +4742,71 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E66" s="3">
         <v>75300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>69100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>62700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>56700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>64500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>65200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>64900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>61400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>63700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>66600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33400</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4911,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,65 +5156,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-73700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-73900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-77000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-74600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-69300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-66400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-66500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-62400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-58500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-55700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-56000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-50400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>22600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5059,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,68 +5464,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>178700</v>
+      </c>
+      <c r="E76" s="3">
         <v>178900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>175700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>177900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>182400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>186100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>191900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>195200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>198800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>197800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>203000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>286900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>289300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>283800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>279900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>277700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>268800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>227300</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5355,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,73 +5618,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,68 +5700,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
         <v>3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-76700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1800</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5582,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,19 +5808,20 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>800</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>700</v>
       </c>
       <c r="G83" s="3">
         <v>700</v>
@@ -5631,25 +5830,25 @@
         <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
         <v>800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>4200</v>
       </c>
       <c r="P83" s="3">
         <v>4200</v>
@@ -5658,20 +5857,20 @@
         <v>4200</v>
       </c>
       <c r="R83" s="3">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="S83" s="3">
         <v>4700</v>
       </c>
       <c r="T83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="U83" s="3">
         <v>5100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5400</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5684,8 +5883,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,68 +6268,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6128,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,68 +6376,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1600</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-1900</v>
       </c>
       <c r="O91" s="3">
         <v>-1900</v>
       </c>
       <c r="P91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-1000</v>
       </c>
       <c r="R91" s="3">
         <v>-1000</v>
       </c>
       <c r="S91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-900</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,8 +6451,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,68 +6605,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6452,8 +6682,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6506,8 +6740,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6554,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,68 +7019,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-800</v>
+        <v>-1200</v>
       </c>
       <c r="E100" s="3">
         <v>-800</v>
       </c>
       <c r="F100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>17400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>31100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6850,8 +7096,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6876,8 +7125,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6924,68 +7173,71 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>33900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6996,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>AOUT</t>
   </si>
@@ -656,105 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,71 +767,74 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E8" s="3">
         <v>58500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>60200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>46300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>53400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>57900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>43400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>42200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>50900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>43700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>45900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>70800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>60800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>64500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>82600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>79100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>50500</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,71 +847,74 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E9" s="3">
         <v>32400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>38000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>37700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>31800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>35800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>45300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>42000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26700</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,71 +927,74 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E10" s="3">
         <v>26100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>18900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>32100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>33100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>29000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>28700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>37300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>37100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23800</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -998,8 +1007,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,71 +1039,72 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1900</v>
+        <v>2200</v>
       </c>
       <c r="E12" s="3">
         <v>1900</v>
       </c>
       <c r="F12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G12" s="3">
         <v>1700</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1800</v>
       </c>
       <c r="H12" s="3">
         <v>1800</v>
       </c>
       <c r="I12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J12" s="3">
         <v>1700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1600</v>
       </c>
       <c r="M12" s="3">
         <v>1600</v>
       </c>
       <c r="N12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1500</v>
       </c>
       <c r="R12" s="3">
         <v>1500</v>
       </c>
       <c r="S12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1200</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1117,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,8 +1197,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1207,11 +1226,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1219,12 +1238,12 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>67800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1240,8 +1259,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1258,25 +1277,28 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E15" s="3">
         <v>3200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3300</v>
       </c>
       <c r="F15" s="3">
         <v>3300</v>
       </c>
       <c r="G15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H15" s="3">
         <v>4200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4000</v>
       </c>
       <c r="I15" s="3">
         <v>4000</v>
@@ -1288,7 +1310,7 @@
         <v>4000</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1335,8 +1357,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,71 +1386,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E17" s="3">
         <v>58200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>57200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>44200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>56300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>58000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>53900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>49200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>116700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>65400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>65500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>56500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>63200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>72500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>69500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>48000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,71 +1464,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-70800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2500</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1544,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,8 +1576,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1553,46 +1586,46 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
@@ -1601,14 +1634,14 @@
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,71 +1654,74 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E21" s="3">
         <v>3500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-66200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,38 +1734,41 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>-100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1775,71 +1814,74 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2900</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-70600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2900</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1852,71 +1894,74 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +1974,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,71 +2054,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-76700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1800</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,71 +2134,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-76700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2160,8 +2214,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2294,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2374,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2454,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,8 +2534,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2477,46 +2546,46 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
@@ -2525,14 +2594,14 @@
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,71 +2614,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-76700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2694,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,71 +2774,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-76700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2776,76 +2854,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2939,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2971,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,70 +3001,71 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E41" s="3">
         <v>17100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>32600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>56300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>60800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>33900</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
+      <c r="W41" s="3">
+        <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
@@ -2993,8 +3079,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3070,71 +3159,74 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E43" s="3">
         <v>31900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>43500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>26600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>25000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>30100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>49800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>33500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>42400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>56100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>58000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>42100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3147,71 +3239,74 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>105400</v>
+      </c>
+      <c r="E44" s="3">
         <v>116400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>113000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>108800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>97600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>103800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>112700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>110000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>104000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>105500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>111400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>120600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>121700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>119600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>105000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>92000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>74300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>73700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>73600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>69600</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3319,11 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3253,42 +3351,42 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>9700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,71 +3399,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>171600</v>
+      </c>
+      <c r="E46" s="3">
         <v>168000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>174200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>162300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>155400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>149900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>164300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>156300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>157600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>163400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>172900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>173900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>179800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>198100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>198500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>190900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>179800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>178400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>168300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>115200</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3479,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3407,8 +3511,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3455,71 +3559,74 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E48" s="3">
         <v>43800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>43700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>44600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>35800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>37200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>36400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>36200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>36400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12300</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,71 +3639,74 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E49" s="3">
         <v>33800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>37900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>43300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>49200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>52000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>55000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>58100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>60700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>63200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>108100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>111300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>114600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>118000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>121900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>125900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>129700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3719,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3799,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,34 +3879,37 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
       </c>
       <c r="F52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>400</v>
       </c>
       <c r="H52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>500</v>
       </c>
       <c r="J52" s="3">
+        <v>500</v>
+      </c>
+      <c r="K52" s="3">
         <v>600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
@@ -3799,35 +3918,35 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
+        <v>300</v>
+      </c>
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,8 +3959,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,71 +4039,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>246400</v>
+      </c>
+      <c r="E54" s="3">
         <v>245900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>254100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>244800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>240600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>239100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>243700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>239100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>243600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>253200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>266500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>270700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>277800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>351400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>354400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>348700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>341300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>341400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>335400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>260800</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4119,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4151,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,71 +4181,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E57" s="3">
         <v>18400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,8 +4259,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4138,28 +4271,28 @@
         <v>1300</v>
       </c>
       <c r="E58" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F58" s="3">
         <v>1400</v>
       </c>
       <c r="G58" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="H58" s="3">
         <v>1300</v>
       </c>
       <c r="I58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J58" s="3">
         <v>1000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>900</v>
       </c>
       <c r="K58" s="3">
         <v>900</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4206,8 +4339,11 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4221,56 +4357,56 @@
         <v>1400</v>
       </c>
       <c r="G59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>900</v>
       </c>
       <c r="J59" s="3">
         <v>900</v>
       </c>
       <c r="K59" s="3">
+        <v>900</v>
+      </c>
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>20300</v>
       </c>
       <c r="S59" s="3">
         <v>20300</v>
       </c>
       <c r="T59" s="3">
+        <v>20300</v>
+      </c>
+      <c r="U59" s="3">
         <v>22200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,71 +4419,74 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E60" s="3">
         <v>34900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>42600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>23600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>41200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>40400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>36300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>40700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>31000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,50 +4499,53 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E61" s="3">
         <v>32300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9600</v>
-      </c>
-      <c r="M61" s="3">
-        <v>19600</v>
       </c>
       <c r="N61" s="3">
         <v>19600</v>
       </c>
       <c r="O61" s="3">
+        <v>19600</v>
+      </c>
+      <c r="P61" s="3">
         <v>24700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4437,8 +4579,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4457,8 +4602,8 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -4467,41 +4612,41 @@
         <v>0</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>24300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4659,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4739,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4819,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,71 +4899,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E66" s="3">
         <v>67200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>75300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>69100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>62700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>56700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>74800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>64500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>65200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>64900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>61400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>63700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>66600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33400</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4979,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5011,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5089,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5169,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5082,8 +5249,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,68 +5329,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-73700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-73900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-77000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-74600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-69300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-66400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-66500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-62400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-58500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-55700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-56000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-50400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>26300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>22600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5300</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5236,8 +5409,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5489,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5569,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,71 +5649,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>177600</v>
+      </c>
+      <c r="E76" s="3">
         <v>178700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>178900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>175700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>177900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>182400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>186000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>186100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>191900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>195200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>198800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>197800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>203000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>286900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>289300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>283800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>279900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>277700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>268800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>227300</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5729,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,76 +5809,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,71 +5894,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-76700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +5974,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,8 +6006,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5818,13 +6016,13 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
+        <v>800</v>
+      </c>
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
@@ -5833,25 +6031,25 @@
         <v>700</v>
       </c>
       <c r="J83" s="3">
+        <v>700</v>
+      </c>
+      <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>4200</v>
       </c>
       <c r="Q83" s="3">
         <v>4200</v>
@@ -5860,20 +6058,20 @@
         <v>4200</v>
       </c>
       <c r="S83" s="3">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="T83" s="3">
         <v>4700</v>
       </c>
       <c r="U83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="V83" s="3">
         <v>5100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5400</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5886,8 +6084,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6164,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6244,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6324,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6404,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,71 +6484,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E89" s="3">
         <v>5900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>16300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6348,8 +6564,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,71 +6596,72 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-1900</v>
       </c>
       <c r="P91" s="3">
         <v>-1900</v>
       </c>
       <c r="Q91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1800</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-1000</v>
       </c>
       <c r="S91" s="3">
         <v>-1000</v>
       </c>
       <c r="T91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-900</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6454,8 +6674,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6754,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,71 +6834,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6685,8 +6914,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6946,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,8 +6976,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6791,8 +7024,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7104,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7184,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,71 +7264,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1200</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-800</v>
       </c>
       <c r="F100" s="3">
         <v>-800</v>
       </c>
       <c r="G100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>17400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>31100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,8 +7344,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,8 +7376,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7176,71 +7424,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E102" s="3">
         <v>2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-23700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>33900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7502,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AOUT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>AOUT</t>
   </si>
@@ -656,115 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -774,80 +776,86 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>57200</v>
+      </c>
+      <c r="F8" s="3">
         <v>29700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>61900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>58500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>60200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>41600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>46300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>53400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>57900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>43400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>42200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>50900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>54400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>43700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>45900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>70100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>70800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>60800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>64500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>82600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>79100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>50500</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,80 +865,86 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>31100</v>
+      </c>
+      <c r="F9" s="3">
         <v>15800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>36600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>32400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>31300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>22700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>26900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>30600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>31400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>23700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>23100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>26900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>28500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>24600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>25800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>38000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>37700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>31800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>35800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>45300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>42000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>26700</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -940,80 +954,86 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F10" s="3">
         <v>13900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>25300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>26100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>28900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>18900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>19400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>22800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>26500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>19700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>19100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>24000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>25900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>19100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>20100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>32100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>33100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>29000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>28700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>37300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>37100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>23800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1043,14 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1054,80 +1080,82 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F12" s="3">
         <v>2000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1700</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1500</v>
       </c>
       <c r="N12" s="3">
         <v>1600</v>
       </c>
       <c r="O12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P12" s="3">
         <v>1600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R12" s="3">
         <v>1800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1500</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="U12" s="3">
-        <v>700</v>
       </c>
       <c r="V12" s="3">
         <v>1500</v>
       </c>
       <c r="W12" s="3">
+        <v>700</v>
+      </c>
+      <c r="X12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y12" s="3">
         <v>1900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1200</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1137,8 +1165,14 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1220,13 +1254,19 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>3400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1252,27 +1292,27 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>67800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1285,11 +1325,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1303,8 +1343,14 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1312,25 +1358,25 @@
         <v>3000</v>
       </c>
       <c r="E15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G15" s="3">
         <v>3500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>3200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>3300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>3300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>4200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4000</v>
       </c>
       <c r="L15" s="3">
         <v>4000</v>
@@ -1339,10 +1385,10 @@
         <v>4000</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1386,8 +1432,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1414,80 +1466,82 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>55100</v>
+      </c>
+      <c r="F17" s="3">
         <v>36500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>62900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>58200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>57200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>44200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>51800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>56300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>58000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>47500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>46200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>53900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>54600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>49200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>116700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>65400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>65500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>56500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>63200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>72500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>69500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>48000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,80 +1551,86 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>-4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-70800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>4700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>4300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>10100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>9600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1640,14 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1611,8 +1677,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1620,28 +1688,28 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-100</v>
@@ -1650,41 +1718,41 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1694,80 +1762,86 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>6400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-66200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>9100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>10100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>8500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>6100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>14900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>14800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>8300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,47 +1851,53 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>100</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>-100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1860,80 +1940,86 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2900</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-70600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>5900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>4300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>10300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>9700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2900</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,16 +2029,22 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
@@ -1961,62 +2053,62 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-100</v>
       </c>
       <c r="O24" s="3">
         <v>-200</v>
       </c>
       <c r="P24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>6100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>2200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>2400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2026,8 +2118,14 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2109,80 +2207,86 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-76700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>4600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>3500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>7300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1800</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,80 +2296,86 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-76700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>3800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>4600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>3500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>7300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2385,14 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2358,8 +2474,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2441,8 +2563,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2524,8 +2652,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2607,8 +2741,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2616,28 +2756,28 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>100</v>
@@ -2646,41 +2786,41 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,80 +2830,86 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-76700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>3800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>3500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>8000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>7300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2919,14 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2856,80 +3008,86 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-76700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>3800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>3500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>8000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>7300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,85 +3097,91 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3191,14 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3058,8 +3228,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3089,79 +3261,81 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F41" s="3">
         <v>17800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>23400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>14200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>23500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>29700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>15900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>18700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>22000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>21700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>16400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>17500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>19500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>22800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>32600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>56300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>60800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>45500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>33900</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
+      <c r="Z41" s="3">
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
@@ -3172,8 +3346,14 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3255,80 +3435,86 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>40500</v>
+      </c>
+      <c r="F43" s="3">
         <v>21900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>39500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>31900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>43500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>26600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>26000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>27500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>40700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>24800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>28100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>26600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>33800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>25000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>30100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>46100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>49800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>33500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>42400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>56100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>58000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>42100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3338,80 +3524,86 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>124000</v>
+      </c>
+      <c r="F44" s="3">
         <v>126400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>105400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>116400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>113000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>108800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>97600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>103800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>112700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>110000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>104000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>105500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>111400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>120600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>121700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>119600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>105000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>92000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>74300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>73700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>73600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>69600</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3421,13 +3613,19 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>900</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -3456,45 +3654,45 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>9700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>11300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>10800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>8500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>9700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>11200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>9000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3500</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,80 +3702,86 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>171300</v>
+      </c>
+      <c r="F46" s="3">
         <v>169800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>171600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>168000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>174200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>162300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>155400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>149900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>164300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>156300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>157600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>163400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>172900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>173900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>179800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>198100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>198500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>190900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>179800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>178400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>168300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>115200</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,8 +3791,14 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3622,11 +3832,11 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3670,80 +3880,86 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>41800</v>
+      </c>
+      <c r="F48" s="3">
         <v>42500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>43100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>43800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>43700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>44200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>44600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>45400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>32500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>33000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>33700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>34400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>35100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>35800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>34500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>37900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>37200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>35900</v>
-      </c>
-      <c r="U48" s="3">
-        <v>36400</v>
-      </c>
-      <c r="V48" s="3">
-        <v>36200</v>
       </c>
       <c r="W48" s="3">
         <v>36400</v>
       </c>
       <c r="X48" s="3">
+        <v>36200</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>36400</v>
+      </c>
+      <c r="Z48" s="3">
         <v>12300</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3753,80 +3969,86 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>27600</v>
+      </c>
+      <c r="F49" s="3">
         <v>29500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>31400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>33800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>35900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>37900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>40200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>43300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>46400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>49200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>52000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>55000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>58100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>60700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>63200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>108100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>111300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>114600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>118000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>121900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>125900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>129700</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3836,8 +4058,14 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3919,8 +4147,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4002,8 +4236,14 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4014,68 +4254,68 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>300</v>
-      </c>
-      <c r="N52" s="3">
-        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
       </c>
       <c r="P52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q52" s="3">
         <v>300</v>
       </c>
       <c r="R52" s="3">
+        <v>400</v>
+      </c>
+      <c r="S52" s="3">
+        <v>300</v>
+      </c>
+      <c r="T52" s="3">
         <v>7300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>7400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>7200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>7100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>4800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>3600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4085,8 +4325,14 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4168,80 +4414,86 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>240900</v>
+      </c>
+      <c r="F54" s="3">
         <v>241900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>246400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>245900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>254100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>244800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>240600</v>
-      </c>
-      <c r="J54" s="3">
-        <v>239100</v>
-      </c>
-      <c r="K54" s="3">
-        <v>243700</v>
       </c>
       <c r="L54" s="3">
         <v>239100</v>
       </c>
       <c r="M54" s="3">
+        <v>243700</v>
+      </c>
+      <c r="N54" s="3">
+        <v>239100</v>
+      </c>
+      <c r="O54" s="3">
         <v>243600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>253200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>266500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>270700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>277800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>351400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>354400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>348700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>341300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>341400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>335400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>260800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4251,8 +4503,14 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4282,8 +4540,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4313,80 +4573,82 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>18900</v>
+      </c>
+      <c r="F57" s="3">
         <v>23100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>15700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>18400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>25400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>18100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>14200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>17800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>15600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>11500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>10100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>8800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>13500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>13600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>20500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>20100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>20200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>16000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>15800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>19900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>15100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,47 +4658,53 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4479,19 +4747,25 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
-        <v>1400</v>
-      </c>
       <c r="F59" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G59" s="3">
         <v>1400</v>
@@ -4500,59 +4774,59 @@
         <v>1400</v>
       </c>
       <c r="I59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>14000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>14800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>15100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>13400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>20500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>21100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>20300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>20300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>22200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>20800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>15800</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4562,80 +4836,86 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>38900</v>
+      </c>
+      <c r="F60" s="3">
         <v>42200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>36800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>34900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>42600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>36100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>29400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>23000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>34000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>29200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>23000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>24100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>23600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>28600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>27000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>40900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>41200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>40400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>36300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>38100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>40700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>31000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4645,59 +4925,65 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>31600</v>
+      </c>
+      <c r="F61" s="3">
         <v>31900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>31900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>32300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>32600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>33000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>33300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>33600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>23600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>23800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>28700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>19600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>19600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>24700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4728,8 +5014,14 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4754,54 +5046,54 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>24300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>24600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>24800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>23100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>23600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>24000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>24400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>25000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>25600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>25900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4811,8 +5103,14 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4894,8 +5192,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4977,8 +5281,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5060,80 +5370,86 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>70500</v>
+      </c>
+      <c r="F66" s="3">
         <v>74100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>68700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>67200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>75300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>69100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>62700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>56700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>57700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>53000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>51700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>58000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>67700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>72900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>74800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>64500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>65200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>64900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>61400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>63700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>66600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>33400</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5143,8 +5459,14 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5174,8 +5496,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5257,8 +5581,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5340,8 +5670,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5423,8 +5759,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5506,77 +5848,83 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-83500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-81500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-74700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-73700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-73900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-77000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-74600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-69300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-66400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-66500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-62400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-58500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-55700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-50400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>26300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>22600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>18000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>14500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>13300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>5300</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5589,8 +5937,14 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5672,8 +6026,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5755,8 +6115,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5838,80 +6204,86 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>165700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>170400</v>
+      </c>
+      <c r="F76" s="3">
         <v>167800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>177600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>178700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>178900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>175700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>177900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>182400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>186000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>186100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>191900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>195200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>198800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>197800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>203000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>286900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>289300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>283800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>279900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>277700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>268800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>227300</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5921,8 +6293,14 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6004,85 +6382,91 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6092,80 +6476,86 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-76700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>3800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>3500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>8000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>7300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6175,8 +6565,14 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6206,22 +6602,24 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
       </c>
       <c r="G83" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
@@ -6230,56 +6628,56 @@
         <v>700</v>
       </c>
       <c r="J83" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
       </c>
       <c r="L83" s="3">
+        <v>700</v>
+      </c>
+      <c r="M83" s="3">
+        <v>700</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>4300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>4100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>4400</v>
       </c>
       <c r="R83" s="3">
         <v>4200</v>
       </c>
       <c r="S83" s="3">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="T83" s="3">
         <v>4200</v>
       </c>
       <c r="U83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="W83" s="3">
         <v>4700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>4700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>5100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>5400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6289,8 +6687,14 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6372,8 +6776,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6455,8 +6865,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6538,8 +6954,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6621,8 +7043,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6704,80 +7132,86 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>7800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-7900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>14700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>13000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-8400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>6400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>18100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>8200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-22100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-3200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>16300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>12600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>3900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6787,8 +7221,14 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6818,79 +7258,81 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-800</v>
       </c>
       <c r="X91" s="3">
         <v>-900</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>-900</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
@@ -6901,8 +7343,14 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6984,8 +7432,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7067,64 +7521,70 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-400</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-1800</v>
       </c>
       <c r="G94" s="3">
         <v>-500</v>
       </c>
       <c r="H94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-3700</v>
       </c>
       <c r="K94" s="3">
         <v>-700</v>
       </c>
       <c r="L94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-28900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-1100</v>
       </c>
       <c r="V94" s="3">
         <v>-1000</v>
@@ -7135,11 +7595,11 @@
       <c r="X94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>-1000</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
@@ -7150,8 +7610,14 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7181,8 +7647,10 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7216,11 +7684,11 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7264,8 +7732,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7347,8 +7821,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7430,8 +7910,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7513,80 +7999,86 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-7600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-5600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-11800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>17400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-7000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>31100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7596,8 +8088,14 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,11 +8129,11 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7679,80 +8177,86 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-5700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>6400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-9200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-6200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>13800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>7500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-10300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>5400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-9800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-23700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-4500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>15300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>11600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>33900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7760,6 +8264,12 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
